--- a/doctool/test/auto/scenario22/システム機能設計書_サンプル_S22_expected.xlsx
+++ b/doctool/test/auto/scenario22/システム機能設計書_サンプル_S22_expected.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario22\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario21\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74851ADB-FEE4-4550-B7BD-5ED0E19B2FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38948D6A-4D7C-4801-8B36-19AD9411900A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1226,7 +1226,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S22</t>
+    <t>システム機能設計書_サンプル_S21</t>
   </si>
   <si>
     <t>B5</t>
@@ -3188,7 +3188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{548803FF-18AB-4CC4-BD47-D79086AED9AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4627714D-30CE-4819-8B37-29385692E5AE}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3859,14 +3859,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{82A4379E-7014-4858-A18B-47ECE65624E7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{DFA52C60-DA31-455F-8514-A318C0EF3502}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{791FA095-134F-4639-A9E4-66E14E83ACD0}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{C9DCF80E-EB03-4DF5-AED8-94ACEEF6669E}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{84143BC5-92D1-46BE-87D2-EDDEF4410448}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{F49927F9-7751-498F-92E5-65E89EDB3308}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{6FA7666B-7FA0-4EEC-AA61-9563056AC174}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{71D8BE5B-16DC-4CDD-9CB3-C7A82A2CEF37}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>

--- a/doctool/test/auto/scenario22/システム機能設計書_サンプル_S22_expected.xlsx
+++ b/doctool/test/auto/scenario22/システム機能設計書_サンプル_S22_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario21\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario22\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38948D6A-4D7C-4801-8B36-19AD9411900A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217B40CC-C081-48FB-B227-88A09728424C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー結果1回目" sheetId="9" r:id="rId1"/>
@@ -1226,7 +1226,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S21</t>
+    <t>システム機能設計書_サンプル_S22</t>
   </si>
   <si>
     <t>B5</t>
@@ -3188,7 +3188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4627714D-30CE-4819-8B37-29385692E5AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7642435-101D-4178-A5CA-8F8E4FA1731E}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3859,14 +3859,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{DFA52C60-DA31-455F-8514-A318C0EF3502}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K18" xr:uid="{10E5C7DB-14B5-4E13-89D6-82BF5616B258}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{F49927F9-7751-498F-92E5-65E89EDB3308}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{6FA7666B-7FA0-4EEC-AA61-9563056AC174}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{71D8BE5B-16DC-4CDD-9CB3-C7A82A2CEF37}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{852815BE-DFAF-4E0A-B793-EE7EAFCF3442}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{E92E1CE4-3187-4344-8EE1-1F46F4ADAB7B}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{E4850918-8ADD-4FB3-9B56-B5590298D95B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
